--- a/planilhas/Auditoria de Google Meu Negócio - V4.xlsx
+++ b/planilhas/Auditoria de Google Meu Negócio - V4.xlsx
@@ -735,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1655,17 +1655,127 @@
       </c>
       <c r="H32" s="9" t="inlineStr"/>
     </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>1.6 Copy do perfil e das respostas</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Primeira linha da descrição vende, não só descreve</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Leia só a primeira linha da descrição — é o que aparece antes do 'ver mais'. Ela diz o que o negócio resolve e para quem, ou começa com 'fundada em 1998, a empresa...'?</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Primeira linha com o que resolve + para quem</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Reescreva começando pelo benefício e pela especialidade; deixe história e fundação para o fim do texto.</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Resposta a avaliação negativa tratada como copy pública</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Leia as respostas às avaliações ruins. Elas são lidas por quem está decidindo, não por quem reclamou. Resposta padrão copiada, defensiva ou que discute com o cliente afasta mais do que a própria reclamação.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Resposta específica, sem discussão, com encaminhamento</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Responda caso a caso: reconheça o ocorrido, diga o que foi feito e ofereça o canal de resolução. Nunca use o mesmo texto em duas respostas.</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Posts com oferta e próximo passo, não recado interno</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Veja os últimos posts: comunicam algo útil ao cliente (oferta, novidade, prova) com um próximo passo claro, ou são avisos internos e datas comemorativas?</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Post com utilidade + CTA</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Publique com foco em oferta, prova e utilidade, sempre com CTA (ligar, orçar, ver rota). Corte post comemorativo sem função.</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Bom ter</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A22:H22"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G32">
+  <conditionalFormatting sqref="G4:G36">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -1682,7 +1792,7 @@
       <formula>"Pendente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F32">
+  <conditionalFormatting sqref="F4:F36">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
       <formula>"Crítico"</formula>
     </cfRule>
@@ -1693,16 +1803,16 @@
       <formula>"Bom ter"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A32">
+  <conditionalFormatting sqref="A4:A36">
     <cfRule type="expression" priority="9" dxfId="0">
       <formula>A4="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G4:G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G4:G36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>_Listas!$A$1:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="A4:A32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A4:A36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>_Listas!$B$1:$B$1</formula1>
     </dataValidation>
   </dataValidations>
